--- a/site/ADP-Recruiting-Management-Manage-Engine-Service-Desk-Cloud-Integration-Guide/headings.xlsx
+++ b/site/ADP-Recruiting-Management-Manage-Engine-Service-Desk-Cloud-Integration-Guide/headings.xlsx
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Onboarding Ticket Settings</t>
+          <t>Onboarding Ticket</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Transaction Template Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-Manage-Engine-Service-Desk-Cloud-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-Manage-Engine-Service-Desk-Cloud-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-Manage-Engine-Service-Desk-Cloud-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-Manage-Engine-Service-Desk-Cloud-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-Manage-Engine-Service-Desk-Cloud-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-Manage-Engine-Service-Desk-Cloud-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Transaction Template Settings</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-Manage-Engine-Service-Desk-Cloud-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-Manage-Engine-Service-Desk-Cloud-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
